--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91835088</v>
+        <v>91835068</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>816</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720417.0521248784</v>
+        <v>720696</v>
       </c>
       <c r="R2" t="n">
-        <v>7334789.166806828</v>
+        <v>7334815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91835069</v>
+        <v>91835088</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720484.9920647677</v>
+        <v>720417</v>
       </c>
       <c r="R3" t="n">
-        <v>7334781.816571528</v>
+        <v>7334789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,16 +872,11 @@
         <v>91835054</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720563.1020084495</v>
+        <v>720563</v>
       </c>
       <c r="R4" t="n">
-        <v>7334816.859725021</v>
+        <v>7334817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91835068</v>
+        <v>91835069</v>
       </c>
       <c r="B5" t="n">
-        <v>86298</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>816</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720695.9417085589</v>
+        <v>720485</v>
       </c>
       <c r="R5" t="n">
-        <v>7334814.981619477</v>
+        <v>7334782</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1066,7 @@
         <v>91835063</v>
       </c>
       <c r="B6" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720426.0164775535</v>
+        <v>720426</v>
       </c>
       <c r="R6" t="n">
-        <v>7334784.155383795</v>
+        <v>7334784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY148"/>
+  <dimension ref="A1:AY147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7522,6 +7522,9 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Tellejokk, Lu lm</t>
@@ -7582,6 +7585,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -10382,48 +10386,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135404408</v>
+        <v>91835063</v>
       </c>
       <c r="B93" t="n">
-        <v>93275</v>
+        <v>92841</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4365</v>
+        <v>4745</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>720391</v>
+        <v>720426</v>
       </c>
       <c r="R93" t="n">
-        <v>7334748</v>
+        <v>7334784</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10447,22 +10451,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10477,60 +10471,60 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>91835063</v>
+        <v>135402504</v>
       </c>
       <c r="B94" t="n">
-        <v>92841</v>
+        <v>91937</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4745</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>720426</v>
+        <v>720384</v>
       </c>
       <c r="R94" t="n">
-        <v>7334784</v>
+        <v>7334806</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10554,12 +10548,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10574,7 +10578,7 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
@@ -10586,10 +10590,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135402504</v>
+        <v>135403670</v>
       </c>
       <c r="B95" t="n">
-        <v>91937</v>
+        <v>93300</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10597,37 +10601,33 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>5449</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>720384</v>
+        <v>720595</v>
       </c>
       <c r="R95" t="n">
-        <v>7334806</v>
+        <v>7334828</v>
       </c>
       <c r="S95" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10681,22 +10681,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135403670</v>
+        <v>135408010</v>
       </c>
       <c r="B96" t="n">
-        <v>93300</v>
+        <v>79397</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10704,33 +10704,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5449</v>
+        <v>6434</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejock, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>720595</v>
+        <v>720522</v>
       </c>
       <c r="R96" t="n">
-        <v>7334828</v>
+        <v>7334895</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10759,7 +10763,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10769,7 +10773,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10784,19 +10788,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135408010</v>
+        <v>135408016</v>
       </c>
       <c r="B97" t="n">
         <v>79397</v>
@@ -10831,10 +10835,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>720522</v>
+        <v>720619</v>
       </c>
       <c r="R97" t="n">
-        <v>7334895</v>
+        <v>7334906</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10866,7 +10870,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10876,7 +10880,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10903,48 +10907,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135408016</v>
+        <v>135402521</v>
       </c>
       <c r="B98" t="n">
-        <v>79397</v>
+        <v>78776</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Tellejock, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>720619</v>
+        <v>720613</v>
       </c>
       <c r="R98" t="n">
-        <v>7334906</v>
+        <v>7334924</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10973,7 +10977,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10983,7 +10987,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10998,19 +11002,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135402521</v>
+        <v>135403892</v>
       </c>
       <c r="B99" t="n">
         <v>78776</v>
@@ -11045,13 +11049,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>720613</v>
+        <v>720401</v>
       </c>
       <c r="R99" t="n">
-        <v>7334924</v>
+        <v>7334796</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11080,7 +11084,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11090,7 +11094,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11105,19 +11109,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135403892</v>
+        <v>135403902</v>
       </c>
       <c r="B100" t="n">
         <v>78776</v>
@@ -11152,13 +11156,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>720401</v>
+        <v>720614</v>
       </c>
       <c r="R100" t="n">
-        <v>7334796</v>
+        <v>7334924</v>
       </c>
       <c r="S100" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11187,7 +11191,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11197,7 +11201,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11224,7 +11228,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135403902</v>
+        <v>135404009</v>
       </c>
       <c r="B101" t="n">
         <v>78776</v>
@@ -11255,17 +11259,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>720614</v>
+        <v>720543</v>
       </c>
       <c r="R101" t="n">
-        <v>7334924</v>
+        <v>7334859</v>
       </c>
       <c r="S101" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11294,7 +11298,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11304,7 +11308,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11319,19 +11323,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135404009</v>
+        <v>135404427</v>
       </c>
       <c r="B102" t="n">
         <v>78776</v>
@@ -11366,13 +11370,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>720543</v>
+        <v>720374</v>
       </c>
       <c r="R102" t="n">
-        <v>7334859</v>
+        <v>7334718</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11401,7 +11405,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11411,7 +11415,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11426,19 +11430,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135404427</v>
+        <v>135404436</v>
       </c>
       <c r="B103" t="n">
         <v>78776</v>
@@ -11473,13 +11477,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>720374</v>
+        <v>720494</v>
       </c>
       <c r="R103" t="n">
-        <v>7334718</v>
+        <v>7334880</v>
       </c>
       <c r="S103" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11508,7 +11512,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11518,7 +11522,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11545,7 +11549,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135404436</v>
+        <v>135404439</v>
       </c>
       <c r="B104" t="n">
         <v>78776</v>
@@ -11580,10 +11584,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>720494</v>
+        <v>720620</v>
       </c>
       <c r="R104" t="n">
-        <v>7334880</v>
+        <v>7334891</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11615,7 +11619,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11625,7 +11629,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11652,10 +11656,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135404439</v>
+        <v>135403900</v>
       </c>
       <c r="B105" t="n">
-        <v>78776</v>
+        <v>79130</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11663,37 +11667,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>720620</v>
+        <v>720528</v>
       </c>
       <c r="R105" t="n">
-        <v>7334891</v>
+        <v>7334892</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11722,7 +11726,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11732,7 +11736,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11747,19 +11751,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135403900</v>
+        <v>135404007</v>
       </c>
       <c r="B106" t="n">
         <v>79130</v>
@@ -11790,17 +11794,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>720528</v>
+        <v>720545</v>
       </c>
       <c r="R106" t="n">
-        <v>7334892</v>
+        <v>7334858</v>
       </c>
       <c r="S106" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11829,7 +11833,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11839,7 +11843,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11854,22 +11858,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135404007</v>
+        <v>135402513</v>
       </c>
       <c r="B107" t="n">
-        <v>79130</v>
+        <v>79992</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11877,37 +11881,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>720545</v>
+        <v>720493</v>
       </c>
       <c r="R107" t="n">
-        <v>7334858</v>
+        <v>7334971</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11936,7 +11940,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11946,7 +11950,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11961,19 +11965,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135402513</v>
+        <v>135402520</v>
       </c>
       <c r="B108" t="n">
         <v>79992</v>
@@ -12008,13 +12012,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>720493</v>
+        <v>720593</v>
       </c>
       <c r="R108" t="n">
-        <v>7334971</v>
+        <v>7334931</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12043,7 +12047,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12053,7 +12057,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12080,7 +12084,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135402520</v>
+        <v>135403675</v>
       </c>
       <c r="B109" t="n">
         <v>79992</v>
@@ -12111,17 +12115,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>720593</v>
+        <v>720312</v>
       </c>
       <c r="R109" t="n">
-        <v>7334931</v>
+        <v>7334757</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12150,7 +12154,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12160,7 +12164,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12175,19 +12179,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135403675</v>
+        <v>135403869</v>
       </c>
       <c r="B110" t="n">
         <v>79992</v>
@@ -12218,17 +12222,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>720312</v>
+        <v>720330</v>
       </c>
       <c r="R110" t="n">
-        <v>7334757</v>
+        <v>7334809</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12257,7 +12261,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12267,7 +12271,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12282,19 +12286,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135403869</v>
+        <v>135403891</v>
       </c>
       <c r="B111" t="n">
         <v>79992</v>
@@ -12329,13 +12333,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>720330</v>
+        <v>720410</v>
       </c>
       <c r="R111" t="n">
-        <v>7334809</v>
+        <v>7334715</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12364,7 +12368,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12374,7 +12378,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12401,7 +12405,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135403891</v>
+        <v>135403907</v>
       </c>
       <c r="B112" t="n">
         <v>79992</v>
@@ -12436,10 +12440,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>720410</v>
+        <v>720673</v>
       </c>
       <c r="R112" t="n">
-        <v>7334715</v>
+        <v>7334860</v>
       </c>
       <c r="S112" t="n">
         <v>14</v>
@@ -12471,7 +12475,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12481,7 +12485,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12508,7 +12512,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135403907</v>
+        <v>135403908</v>
       </c>
       <c r="B113" t="n">
         <v>79992</v>
@@ -12543,13 +12547,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>720673</v>
+        <v>720498</v>
       </c>
       <c r="R113" t="n">
-        <v>7334860</v>
+        <v>7334772</v>
       </c>
       <c r="S113" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12578,7 +12582,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12588,7 +12592,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12615,7 +12619,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135403908</v>
+        <v>135404006</v>
       </c>
       <c r="B114" t="n">
         <v>79992</v>
@@ -12646,17 +12650,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>720498</v>
+        <v>720432</v>
       </c>
       <c r="R114" t="n">
-        <v>7334772</v>
+        <v>7334778</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12685,7 +12689,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12695,7 +12699,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12710,19 +12714,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135404006</v>
+        <v>135404010</v>
       </c>
       <c r="B115" t="n">
         <v>79992</v>
@@ -12757,13 +12761,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>720432</v>
+        <v>720546</v>
       </c>
       <c r="R115" t="n">
-        <v>7334778</v>
+        <v>7334858</v>
       </c>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12792,7 +12796,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12802,7 +12806,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12829,7 +12833,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135404010</v>
+        <v>135404011</v>
       </c>
       <c r="B116" t="n">
         <v>79992</v>
@@ -12864,10 +12868,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>720546</v>
+        <v>720584</v>
       </c>
       <c r="R116" t="n">
-        <v>7334858</v>
+        <v>7334889</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12899,7 +12903,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12909,7 +12913,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12936,7 +12940,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135404011</v>
+        <v>135404430</v>
       </c>
       <c r="B117" t="n">
         <v>79992</v>
@@ -12971,13 +12975,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>720584</v>
+        <v>720463</v>
       </c>
       <c r="R117" t="n">
-        <v>7334889</v>
+        <v>7334846</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13006,7 +13010,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13016,7 +13020,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13031,19 +13035,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135404430</v>
+        <v>135404435</v>
       </c>
       <c r="B118" t="n">
         <v>79992</v>
@@ -13078,13 +13082,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>720463</v>
+        <v>720491</v>
       </c>
       <c r="R118" t="n">
-        <v>7334846</v>
+        <v>7334882</v>
       </c>
       <c r="S118" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13113,7 +13117,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13123,7 +13127,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13150,7 +13154,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135404435</v>
+        <v>135408028</v>
       </c>
       <c r="B119" t="n">
         <v>79992</v>
@@ -13181,14 +13185,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejock, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>720491</v>
+        <v>720296</v>
       </c>
       <c r="R119" t="n">
-        <v>7334882</v>
+        <v>7334795</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13220,7 +13224,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13230,7 +13234,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13245,22 +13249,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135408028</v>
+        <v>135403903</v>
       </c>
       <c r="B120" t="n">
-        <v>79992</v>
+        <v>78377</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13268,37 +13272,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Tellejock, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>720296</v>
+        <v>720621</v>
       </c>
       <c r="R120" t="n">
-        <v>7334795</v>
+        <v>7334941</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13327,7 +13331,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13337,7 +13341,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13352,22 +13356,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135403903</v>
+        <v>135402507</v>
       </c>
       <c r="B121" t="n">
-        <v>78377</v>
+        <v>57975</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13375,37 +13379,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>720621</v>
+        <v>720444</v>
       </c>
       <c r="R121" t="n">
-        <v>7334941</v>
+        <v>7334865</v>
       </c>
       <c r="S121" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13434,7 +13443,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13444,7 +13453,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13459,19 +13468,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135402507</v>
+        <v>135402516</v>
       </c>
       <c r="B122" t="n">
         <v>57975</v>
@@ -13511,13 +13520,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>720444</v>
+        <v>720501</v>
       </c>
       <c r="R122" t="n">
-        <v>7334865</v>
+        <v>7335071</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13546,7 +13555,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13556,7 +13565,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13583,7 +13592,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135402516</v>
+        <v>135404441</v>
       </c>
       <c r="B123" t="n">
         <v>57975</v>
@@ -13612,24 +13621,19 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>720501</v>
+        <v>720643</v>
       </c>
       <c r="R123" t="n">
-        <v>7335071</v>
+        <v>7334801</v>
       </c>
       <c r="S123" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13658,7 +13662,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13668,7 +13672,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13683,44 +13692,44 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135404441</v>
+        <v>135404422</v>
       </c>
       <c r="B124" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13730,10 +13739,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>720643</v>
+        <v>720323</v>
       </c>
       <c r="R124" t="n">
-        <v>7334801</v>
+        <v>7334836</v>
       </c>
       <c r="S124" t="n">
         <v>6</v>
@@ -13765,7 +13774,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13775,12 +13784,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13807,48 +13811,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135404422</v>
+        <v>135403904</v>
       </c>
       <c r="B125" t="n">
-        <v>57162</v>
+        <v>79131</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>720323</v>
+        <v>720618</v>
       </c>
       <c r="R125" t="n">
-        <v>7334836</v>
+        <v>7334938</v>
       </c>
       <c r="S125" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13877,7 +13881,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13887,7 +13891,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13902,19 +13906,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135403904</v>
+        <v>135404008</v>
       </c>
       <c r="B126" t="n">
         <v>79131</v>
@@ -13945,17 +13949,17 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>720618</v>
+        <v>720545</v>
       </c>
       <c r="R126" t="n">
-        <v>7334938</v>
+        <v>7334857</v>
       </c>
       <c r="S126" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13984,7 +13988,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13994,7 +13998,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14009,19 +14013,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135404008</v>
+        <v>135408146</v>
       </c>
       <c r="B127" t="n">
         <v>79131</v>
@@ -14056,13 +14060,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>720545</v>
+        <v>720563</v>
       </c>
       <c r="R127" t="n">
-        <v>7334857</v>
+        <v>7334800</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14091,7 +14095,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14101,7 +14105,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14116,22 +14120,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135408146</v>
+        <v>135404438</v>
       </c>
       <c r="B128" t="n">
-        <v>79131</v>
+        <v>79963</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14139,21 +14143,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14163,13 +14167,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>720563</v>
+        <v>720619</v>
       </c>
       <c r="R128" t="n">
-        <v>7334800</v>
+        <v>7334893</v>
       </c>
       <c r="S128" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14198,7 +14202,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14208,7 +14212,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14223,22 +14227,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135404438</v>
+        <v>135402511</v>
       </c>
       <c r="B129" t="n">
-        <v>79963</v>
+        <v>79396</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14246,37 +14250,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>720619</v>
+        <v>720505</v>
       </c>
       <c r="R129" t="n">
-        <v>7334893</v>
+        <v>7334962</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14305,7 +14309,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14315,7 +14319,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14330,19 +14334,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135402511</v>
+        <v>135402514</v>
       </c>
       <c r="B130" t="n">
         <v>79396</v>
@@ -14377,13 +14381,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>720505</v>
+        <v>720484</v>
       </c>
       <c r="R130" t="n">
-        <v>7334962</v>
+        <v>7335019</v>
       </c>
       <c r="S130" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14412,7 +14416,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14422,7 +14426,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14449,7 +14453,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135402514</v>
+        <v>135402517</v>
       </c>
       <c r="B131" t="n">
         <v>79396</v>
@@ -14484,13 +14488,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>720484</v>
+        <v>720553</v>
       </c>
       <c r="R131" t="n">
-        <v>7335019</v>
+        <v>7334949</v>
       </c>
       <c r="S131" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14519,7 +14523,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14529,7 +14533,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14556,7 +14560,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135402517</v>
+        <v>135402524</v>
       </c>
       <c r="B132" t="n">
         <v>79396</v>
@@ -14591,13 +14595,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>720553</v>
+        <v>720608</v>
       </c>
       <c r="R132" t="n">
-        <v>7334949</v>
+        <v>7334845</v>
       </c>
       <c r="S132" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14626,7 +14630,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14636,7 +14640,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14663,7 +14667,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135402524</v>
+        <v>135402533</v>
       </c>
       <c r="B133" t="n">
         <v>79396</v>
@@ -14698,13 +14702,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>720608</v>
+        <v>720455</v>
       </c>
       <c r="R133" t="n">
-        <v>7334845</v>
+        <v>7334723</v>
       </c>
       <c r="S133" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14733,7 +14737,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14743,7 +14747,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14770,7 +14774,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135402533</v>
+        <v>135404013</v>
       </c>
       <c r="B134" t="n">
         <v>79396</v>
@@ -14801,17 +14805,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>720455</v>
+        <v>720630</v>
       </c>
       <c r="R134" t="n">
-        <v>7334723</v>
+        <v>7334922</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14840,7 +14844,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14850,7 +14854,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14865,19 +14869,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135404013</v>
+        <v>135404419</v>
       </c>
       <c r="B135" t="n">
         <v>79396</v>
@@ -14912,13 +14916,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>720630</v>
+        <v>720268</v>
       </c>
       <c r="R135" t="n">
-        <v>7334922</v>
+        <v>7334851</v>
       </c>
       <c r="S135" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14947,7 +14951,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14957,7 +14961,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14972,19 +14976,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135404419</v>
+        <v>135404442</v>
       </c>
       <c r="B136" t="n">
         <v>79396</v>
@@ -15019,13 +15023,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>720268</v>
+        <v>720594</v>
       </c>
       <c r="R136" t="n">
-        <v>7334851</v>
+        <v>7334841</v>
       </c>
       <c r="S136" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15054,7 +15058,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15064,7 +15068,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15091,7 +15095,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135404442</v>
+        <v>135408015</v>
       </c>
       <c r="B137" t="n">
         <v>79396</v>
@@ -15122,17 +15126,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejock, Lu lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>720594</v>
+        <v>720618</v>
       </c>
       <c r="R137" t="n">
-        <v>7334841</v>
+        <v>7334911</v>
       </c>
       <c r="S137" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15161,7 +15165,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15171,7 +15175,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15186,19 +15190,19 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135408015</v>
+        <v>135408025</v>
       </c>
       <c r="B138" t="n">
         <v>79396</v>
@@ -15233,13 +15237,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>720618</v>
+        <v>720392</v>
       </c>
       <c r="R138" t="n">
-        <v>7334911</v>
+        <v>7334751</v>
       </c>
       <c r="S138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15268,7 +15272,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15278,7 +15282,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15305,7 +15309,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135408025</v>
+        <v>135408145</v>
       </c>
       <c r="B139" t="n">
         <v>79396</v>
@@ -15336,14 +15340,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Tellejock, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>720392</v>
+        <v>720523</v>
       </c>
       <c r="R139" t="n">
-        <v>7334751</v>
+        <v>7334812</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15375,7 +15379,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15385,7 +15389,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15400,19 +15404,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135408145</v>
+        <v>135408147</v>
       </c>
       <c r="B140" t="n">
         <v>79396</v>
@@ -15447,10 +15451,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>720523</v>
+        <v>720572</v>
       </c>
       <c r="R140" t="n">
-        <v>7334812</v>
+        <v>7334764</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15482,7 +15486,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15492,7 +15496,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15519,48 +15523,43 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135408147</v>
+        <v>135403871</v>
       </c>
       <c r="B141" t="n">
-        <v>79396</v>
+        <v>80267</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
+        <v>266179</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lecidea subhumida</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Vain.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>720572</v>
+        <v>720335</v>
       </c>
       <c r="R141" t="n">
-        <v>7334764</v>
+        <v>7334818</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15589,7 +15588,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15599,7 +15598,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15614,19 +15613,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135403871</v>
+        <v>135403897</v>
       </c>
       <c r="B142" t="n">
         <v>80267</v>
@@ -15656,13 +15655,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>720335</v>
+        <v>720503</v>
       </c>
       <c r="R142" t="n">
-        <v>7334818</v>
+        <v>7334857</v>
       </c>
       <c r="S142" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15691,7 +15690,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15701,7 +15700,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15728,7 +15727,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135403897</v>
+        <v>135403910</v>
       </c>
       <c r="B143" t="n">
         <v>80267</v>
@@ -15758,13 +15757,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>720503</v>
+        <v>720472</v>
       </c>
       <c r="R143" t="n">
-        <v>7334857</v>
+        <v>7334716</v>
       </c>
       <c r="S143" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15793,7 +15792,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15803,7 +15802,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15830,43 +15834,48 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135403910</v>
+        <v>135404019</v>
       </c>
       <c r="B144" t="n">
-        <v>80267</v>
+        <v>92365</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>266179</v>
+        <v>6040162</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>720472</v>
+        <v>720410</v>
       </c>
       <c r="R144" t="n">
-        <v>7334716</v>
+        <v>7334743</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15895,7 +15904,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15905,12 +15914,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15919,28 +15923,29 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135404019</v>
+        <v>135403671</v>
       </c>
       <c r="B145" t="n">
-        <v>92365</v>
+        <v>93292</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15948,21 +15953,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6040162</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Tallkötticka</t>
-        </is>
+        <v>6331648</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon aquiloniniger</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15972,13 +15972,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>720410</v>
+        <v>720595</v>
       </c>
       <c r="R145" t="n">
-        <v>7334743</v>
+        <v>7334830</v>
       </c>
       <c r="S145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16026,26 +16026,25 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135403671</v>
+        <v>135403898</v>
       </c>
       <c r="B146" t="n">
         <v>93292</v>
@@ -16071,17 +16070,17 @@
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>720595</v>
+        <v>720508</v>
       </c>
       <c r="R146" t="n">
-        <v>7334830</v>
+        <v>7334876</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16110,7 +16109,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16120,7 +16119,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16135,19 +16134,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135403898</v>
+        <v>135404016</v>
       </c>
       <c r="B147" t="n">
         <v>93292</v>
@@ -16173,17 +16172,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>720508</v>
+        <v>720643</v>
       </c>
       <c r="R147" t="n">
-        <v>7334876</v>
+        <v>7334792</v>
       </c>
       <c r="S147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16212,7 +16211,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16222,7 +16221,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16237,117 +16236,15 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>135404016</v>
-      </c>
-      <c r="B148" t="n">
-        <v>93292</v>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>6331648</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Phellodon aquiloniniger</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Tellejokk, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q148" t="n">
-        <v>720643</v>
-      </c>
-      <c r="R148" t="n">
-        <v>7334792</v>
-      </c>
-      <c r="S148" t="n">
-        <v>5</v>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AD148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT148" t="inlineStr"/>
-      <c r="AW148" t="inlineStr">
-        <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AX148" t="inlineStr">
-        <is>
-          <t>Christina Boyd, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -9559,6 +9559,9 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>tellejåkk juli 2026, Lu lm</t>
@@ -9619,6 +9622,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9630,7 +9634,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9666,6 +9670,9 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>tellejåkk juli 2026, Lu lm</t>
@@ -9726,6 +9733,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9737,7 +9745,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -9316,7 +9316,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135408148</v>
+        <v>135410054</v>
       </c>
       <c r="B83" t="n">
         <v>93271</v>
@@ -9347,17 +9347,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>tellejåkk juli 2026, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>720511</v>
+        <v>720483</v>
       </c>
       <c r="R83" t="n">
-        <v>7334745</v>
+        <v>7334855</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9411,19 +9411,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135410054</v>
+        <v>135410055</v>
       </c>
       <c r="B84" t="n">
         <v>93271</v>
@@ -9452,19 +9452,22 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>tellejåkk juli 2026, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>720483</v>
+        <v>720642</v>
       </c>
       <c r="R84" t="n">
-        <v>7334855</v>
+        <v>7334792</v>
       </c>
       <c r="S84" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9493,7 +9496,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9503,7 +9506,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9512,6 +9515,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9523,14 +9527,14 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135410055</v>
+        <v>135410056</v>
       </c>
       <c r="B85" t="n">
         <v>93271</v>
@@ -9568,13 +9572,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>720642</v>
+        <v>720622</v>
       </c>
       <c r="R85" t="n">
-        <v>7334792</v>
+        <v>7334812</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9603,7 +9607,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9613,7 +9617,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9641,7 +9645,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135410056</v>
+        <v>135504175</v>
       </c>
       <c r="B86" t="n">
         <v>93271</v>
@@ -9670,22 +9674,19 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>tellejåkk juli 2026, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>720622</v>
+        <v>720511</v>
       </c>
       <c r="R86" t="n">
-        <v>7334812</v>
+        <v>7334745</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9714,7 +9715,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9724,7 +9725,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9733,19 +9734,18 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -14033,7 +14033,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135408146</v>
+        <v>135504173</v>
       </c>
       <c r="B127" t="n">
         <v>79131</v>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY147"/>
+  <dimension ref="A1:AZ147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404433</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403886</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403890</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403893</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403912</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404432</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404446</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408019</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835068</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404434</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403885</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404423</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404444</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403999</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404431</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2481,6 +2566,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408020</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408026</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2695,6 +2790,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403674</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835088</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2909,6 +3014,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408029</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3006,6 +3116,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835054</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3103,6 +3218,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835069</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3210,6 +3330,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402506</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3317,6 +3442,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402508</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3424,6 +3554,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402510</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3531,6 +3666,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402512</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3638,6 +3778,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402515</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3745,6 +3890,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402518</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3852,6 +4002,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402519</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3959,6 +4114,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402522</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4066,6 +4226,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402523</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4173,6 +4338,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402525</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4280,6 +4450,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402526</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4387,6 +4562,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402527</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4494,6 +4674,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402528</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4601,6 +4786,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402530</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4708,6 +4898,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402531</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4815,6 +5010,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402532</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4922,6 +5122,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403667</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5029,6 +5234,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403672</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5136,6 +5346,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403868</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5243,6 +5458,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403870</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5350,6 +5570,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403872</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5457,6 +5682,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403873</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5564,6 +5794,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403876</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5671,6 +5906,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403878</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5778,6 +6018,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403881</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5885,6 +6130,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403884</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5992,6 +6242,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403894</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6099,6 +6354,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403896</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6206,6 +6466,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403899</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6313,6 +6578,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403901</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6420,6 +6690,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403909</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6527,6 +6802,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403911</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6634,6 +6914,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404004</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6741,6 +7026,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404005</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6848,6 +7138,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404014</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6955,6 +7250,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404015</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7062,6 +7362,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404018</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7169,6 +7474,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404420</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7276,6 +7586,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404421</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7383,6 +7698,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404424</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7490,6 +7810,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404425</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7601,6 +7926,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404426</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7708,6 +8038,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404428</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7815,6 +8150,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404429</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7922,6 +8262,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404437</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8029,6 +8374,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404440</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8136,6 +8486,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404443</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8243,6 +8598,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408007</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8350,6 +8710,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408008</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8457,6 +8822,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408009</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8564,6 +8934,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408011</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8671,6 +9046,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408012</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8778,6 +9158,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408013</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8885,6 +9270,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408017</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8992,6 +9382,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408018</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9099,6 +9494,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408023</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9206,6 +9606,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408027</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9313,6 +9718,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408143</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9420,6 +9830,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410054</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9531,6 +9946,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410055</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9642,6 +10062,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410056</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9749,6 +10174,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504175</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9856,6 +10286,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403669</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9963,6 +10398,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403874</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10070,6 +10510,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403875</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10177,6 +10622,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403880</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10284,6 +10734,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403889</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10391,6 +10846,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403895</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10488,6 +10948,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835063</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10595,6 +11060,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402504</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10698,6 +11168,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403670</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10805,6 +11280,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408010</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10912,6 +11392,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408016</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11019,6 +11504,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402521</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11126,6 +11616,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403892</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11233,6 +11728,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403902</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11340,6 +11840,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404009</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11447,6 +11952,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404427</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11554,6 +12064,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404436</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11661,6 +12176,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404439</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11768,6 +12288,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403900</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11875,6 +12400,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404007</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11982,6 +12512,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402513</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12089,6 +12624,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402520</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12196,6 +12736,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403675</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12303,6 +12848,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403869</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12410,6 +12960,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403891</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12517,6 +13072,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403907</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12624,6 +13184,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403908</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12731,6 +13296,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404006</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12838,6 +13408,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404010</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12945,6 +13520,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404011</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13052,6 +13632,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404430</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13159,6 +13744,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404435</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13266,6 +13856,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408028</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13373,6 +13968,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403903</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13485,6 +14085,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402507</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13597,6 +14202,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402516</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13709,6 +14319,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404441</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13816,6 +14431,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404422</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13923,6 +14543,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403904</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14030,6 +14655,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404008</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14137,6 +14767,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504173</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14244,6 +14879,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404438</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14351,6 +14991,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402511</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14458,6 +15103,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402514</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14565,6 +15215,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402517</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14672,6 +15327,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402524</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14779,6 +15439,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402533</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14886,6 +15551,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404013</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14993,6 +15663,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404419</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15100,6 +15775,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404442</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15207,6 +15887,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408015</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15314,6 +15999,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408025</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15421,6 +16111,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408145</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15528,6 +16223,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408147</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15630,6 +16330,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403871</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15732,6 +16437,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403897</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15839,6 +16549,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403910</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15947,6 +16662,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404019</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16049,6 +16769,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403671</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16151,6 +16876,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403898</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16253,8 +16983,161 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404016</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135404433</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135404447</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135403886</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135403890</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135403893</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135403912</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135404432</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135404446</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135408019</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135404434</v>
       </c>
       <c r="B12" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>135403885</v>
       </c>
       <c r="B13" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135404423</v>
       </c>
       <c r="B14" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135404444</v>
       </c>
       <c r="B15" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>135403999</v>
       </c>
       <c r="B16" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135404431</v>
       </c>
       <c r="B17" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135408020</v>
       </c>
       <c r="B18" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>135408026</v>
       </c>
       <c r="B19" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135403674</v>
       </c>
       <c r="B20" t="n">
-        <v>93263</v>
+        <v>93305</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135408029</v>
       </c>
       <c r="B22" t="n">
-        <v>93265</v>
+        <v>93307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>135402506</v>
       </c>
       <c r="B25" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>135402508</v>
       </c>
       <c r="B26" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>135402510</v>
       </c>
       <c r="B27" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135402512</v>
       </c>
       <c r="B28" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>135402515</v>
       </c>
       <c r="B29" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135402518</v>
       </c>
       <c r="B30" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>135402519</v>
       </c>
       <c r="B31" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>135402522</v>
       </c>
       <c r="B32" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>135402523</v>
       </c>
       <c r="B33" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>135402525</v>
       </c>
       <c r="B34" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>135402526</v>
       </c>
       <c r="B35" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>135402527</v>
       </c>
       <c r="B36" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135402528</v>
       </c>
       <c r="B37" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>135402530</v>
       </c>
       <c r="B38" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>135402531</v>
       </c>
       <c r="B39" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>135402532</v>
       </c>
       <c r="B40" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>135403667</v>
       </c>
       <c r="B41" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>135403672</v>
       </c>
       <c r="B42" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>135403868</v>
       </c>
       <c r="B43" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>135403870</v>
       </c>
       <c r="B44" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135403872</v>
       </c>
       <c r="B45" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>135403873</v>
       </c>
       <c r="B46" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>135403876</v>
       </c>
       <c r="B47" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>135403878</v>
       </c>
       <c r="B48" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>135403881</v>
       </c>
       <c r="B49" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>135403884</v>
       </c>
       <c r="B50" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135403894</v>
       </c>
       <c r="B51" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>135403896</v>
       </c>
       <c r="B52" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>135403899</v>
       </c>
       <c r="B53" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>135403901</v>
       </c>
       <c r="B54" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135403909</v>
       </c>
       <c r="B55" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135403911</v>
       </c>
       <c r="B56" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>135404004</v>
       </c>
       <c r="B57" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>135404005</v>
       </c>
       <c r="B58" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>135404014</v>
       </c>
       <c r="B59" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>135404015</v>
       </c>
       <c r="B60" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>135404018</v>
       </c>
       <c r="B61" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>135404420</v>
       </c>
       <c r="B62" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>135404421</v>
       </c>
       <c r="B63" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135404424</v>
       </c>
       <c r="B64" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135404425</v>
       </c>
       <c r="B65" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>135404426</v>
       </c>
       <c r="B66" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>135404428</v>
       </c>
       <c r="B67" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135404429</v>
       </c>
       <c r="B68" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>135404437</v>
       </c>
       <c r="B69" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>135404440</v>
       </c>
       <c r="B70" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135404443</v>
       </c>
       <c r="B71" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>135408007</v>
       </c>
       <c r="B72" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>135408008</v>
       </c>
       <c r="B73" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>135408009</v>
       </c>
       <c r="B74" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>135408011</v>
       </c>
       <c r="B75" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135408012</v>
       </c>
       <c r="B76" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>135408013</v>
       </c>
       <c r="B77" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>135408017</v>
       </c>
       <c r="B78" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>135408018</v>
       </c>
       <c r="B79" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>135408023</v>
       </c>
       <c r="B80" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>135408027</v>
       </c>
       <c r="B81" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>135408143</v>
       </c>
       <c r="B82" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>135410054</v>
       </c>
       <c r="B83" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>135410055</v>
       </c>
       <c r="B84" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>135410056</v>
       </c>
       <c r="B85" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>135504175</v>
       </c>
       <c r="B86" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>135403669</v>
       </c>
       <c r="B87" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>135403874</v>
       </c>
       <c r="B88" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>135403875</v>
       </c>
       <c r="B89" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>135403880</v>
       </c>
       <c r="B90" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>135403889</v>
       </c>
       <c r="B91" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>135403895</v>
       </c>
       <c r="B92" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>135402504</v>
       </c>
       <c r="B94" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>135403670</v>
       </c>
       <c r="B95" t="n">
-        <v>93300</v>
+        <v>93342</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>135408010</v>
       </c>
       <c r="B96" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>135408016</v>
       </c>
       <c r="B97" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>135402521</v>
       </c>
       <c r="B98" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>135403892</v>
       </c>
       <c r="B99" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>135403902</v>
       </c>
       <c r="B100" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>135404009</v>
       </c>
       <c r="B101" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>135404427</v>
       </c>
       <c r="B102" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>135404436</v>
       </c>
       <c r="B103" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>135404439</v>
       </c>
       <c r="B104" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>135403900</v>
       </c>
       <c r="B105" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>135404007</v>
       </c>
       <c r="B106" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>135402513</v>
       </c>
       <c r="B107" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>135402520</v>
       </c>
       <c r="B108" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>135403675</v>
       </c>
       <c r="B109" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>135403869</v>
       </c>
       <c r="B110" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>135403891</v>
       </c>
       <c r="B111" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>135403907</v>
       </c>
       <c r="B112" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>135403908</v>
       </c>
       <c r="B113" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>135404006</v>
       </c>
       <c r="B114" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>135404010</v>
       </c>
       <c r="B115" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>135404011</v>
       </c>
       <c r="B116" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>135404430</v>
       </c>
       <c r="B117" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>135404435</v>
       </c>
       <c r="B118" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>135408028</v>
       </c>
       <c r="B119" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>135403903</v>
       </c>
       <c r="B120" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>135402507</v>
       </c>
       <c r="B121" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>135402516</v>
       </c>
       <c r="B122" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>135404441</v>
       </c>
       <c r="B123" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>135404422</v>
       </c>
       <c r="B124" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>135403904</v>
       </c>
       <c r="B125" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>135404008</v>
       </c>
       <c r="B126" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>135504173</v>
       </c>
       <c r="B127" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>135404438</v>
       </c>
       <c r="B128" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>135402511</v>
       </c>
       <c r="B129" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>135402514</v>
       </c>
       <c r="B130" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>135402517</v>
       </c>
       <c r="B131" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>135402524</v>
       </c>
       <c r="B132" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>135402533</v>
       </c>
       <c r="B133" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135404013</v>
       </c>
       <c r="B134" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>135404419</v>
       </c>
       <c r="B135" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>135404442</v>
       </c>
       <c r="B136" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>135408015</v>
       </c>
       <c r="B137" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>135408025</v>
       </c>
       <c r="B138" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>135408145</v>
       </c>
       <c r="B139" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>135408147</v>
       </c>
       <c r="B140" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>135403871</v>
       </c>
       <c r="B141" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>135403897</v>
       </c>
       <c r="B142" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>135403910</v>
       </c>
       <c r="B143" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>135404019</v>
       </c>
       <c r="B144" t="n">
-        <v>92365</v>
+        <v>92407</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>135403671</v>
       </c>
       <c r="B145" t="n">
-        <v>93292</v>
+        <v>93334</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>135403898</v>
       </c>
       <c r="B146" t="n">
-        <v>93292</v>
+        <v>93334</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>135404016</v>
       </c>
       <c r="B147" t="n">
-        <v>93292</v>
+        <v>93334</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135404433</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135404447</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135403886</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135403890</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135403893</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135403912</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135404432</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135404446</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135408019</v>
       </c>
       <c r="B10" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135404434</v>
       </c>
       <c r="B12" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>135403885</v>
       </c>
       <c r="B13" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135404423</v>
       </c>
       <c r="B14" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135404444</v>
       </c>
       <c r="B15" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>135403999</v>
       </c>
       <c r="B16" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135404431</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135408020</v>
       </c>
       <c r="B18" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>135408026</v>
       </c>
       <c r="B19" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135403674</v>
       </c>
       <c r="B20" t="n">
-        <v>93305</v>
+        <v>93332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135408029</v>
       </c>
       <c r="B22" t="n">
-        <v>93307</v>
+        <v>93334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>135402506</v>
       </c>
       <c r="B25" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>135402508</v>
       </c>
       <c r="B26" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>135402510</v>
       </c>
       <c r="B27" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135402512</v>
       </c>
       <c r="B28" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>135402515</v>
       </c>
       <c r="B29" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135402518</v>
       </c>
       <c r="B30" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>135402519</v>
       </c>
       <c r="B31" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>135402522</v>
       </c>
       <c r="B32" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>135402523</v>
       </c>
       <c r="B33" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>135402525</v>
       </c>
       <c r="B34" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>135402526</v>
       </c>
       <c r="B35" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>135402527</v>
       </c>
       <c r="B36" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135402528</v>
       </c>
       <c r="B37" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>135402530</v>
       </c>
       <c r="B38" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>135402531</v>
       </c>
       <c r="B39" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>135402532</v>
       </c>
       <c r="B40" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>135403667</v>
       </c>
       <c r="B41" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>135403672</v>
       </c>
       <c r="B42" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>135403868</v>
       </c>
       <c r="B43" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>135403870</v>
       </c>
       <c r="B44" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135403872</v>
       </c>
       <c r="B45" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>135403873</v>
       </c>
       <c r="B46" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>135403876</v>
       </c>
       <c r="B47" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>135403878</v>
       </c>
       <c r="B48" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>135403881</v>
       </c>
       <c r="B49" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>135403884</v>
       </c>
       <c r="B50" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135403894</v>
       </c>
       <c r="B51" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>135403896</v>
       </c>
       <c r="B52" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>135403899</v>
       </c>
       <c r="B53" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>135403901</v>
       </c>
       <c r="B54" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135403909</v>
       </c>
       <c r="B55" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135403911</v>
       </c>
       <c r="B56" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>135404004</v>
       </c>
       <c r="B57" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>135404005</v>
       </c>
       <c r="B58" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>135404014</v>
       </c>
       <c r="B59" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>135404015</v>
       </c>
       <c r="B60" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>135404018</v>
       </c>
       <c r="B61" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>135404420</v>
       </c>
       <c r="B62" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>135404421</v>
       </c>
       <c r="B63" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135404424</v>
       </c>
       <c r="B64" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135404425</v>
       </c>
       <c r="B65" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>135404426</v>
       </c>
       <c r="B66" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>135404428</v>
       </c>
       <c r="B67" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135404429</v>
       </c>
       <c r="B68" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>135404437</v>
       </c>
       <c r="B69" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>135404440</v>
       </c>
       <c r="B70" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135404443</v>
       </c>
       <c r="B71" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>135408007</v>
       </c>
       <c r="B72" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>135408008</v>
       </c>
       <c r="B73" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>135408009</v>
       </c>
       <c r="B74" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>135408011</v>
       </c>
       <c r="B75" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135408012</v>
       </c>
       <c r="B76" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>135408013</v>
       </c>
       <c r="B77" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>135408017</v>
       </c>
       <c r="B78" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>135408018</v>
       </c>
       <c r="B79" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>135408023</v>
       </c>
       <c r="B80" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>135408027</v>
       </c>
       <c r="B81" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>135408143</v>
       </c>
       <c r="B82" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>135410054</v>
       </c>
       <c r="B83" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>135410055</v>
       </c>
       <c r="B84" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>135410056</v>
       </c>
       <c r="B85" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>135504175</v>
       </c>
       <c r="B86" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>135403669</v>
       </c>
       <c r="B87" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>135403874</v>
       </c>
       <c r="B88" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>135403875</v>
       </c>
       <c r="B89" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>135403880</v>
       </c>
       <c r="B90" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>135403889</v>
       </c>
       <c r="B91" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>135403895</v>
       </c>
       <c r="B92" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>135402504</v>
       </c>
       <c r="B94" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>135403670</v>
       </c>
       <c r="B95" t="n">
-        <v>93342</v>
+        <v>93369</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>135408010</v>
       </c>
       <c r="B96" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>135408016</v>
       </c>
       <c r="B97" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>135402521</v>
       </c>
       <c r="B98" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>135403892</v>
       </c>
       <c r="B99" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>135403902</v>
       </c>
       <c r="B100" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>135404009</v>
       </c>
       <c r="B101" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>135404427</v>
       </c>
       <c r="B102" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>135404436</v>
       </c>
       <c r="B103" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>135404439</v>
       </c>
       <c r="B104" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>135403900</v>
       </c>
       <c r="B105" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>135404007</v>
       </c>
       <c r="B106" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>135402513</v>
       </c>
       <c r="B107" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>135402520</v>
       </c>
       <c r="B108" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>135403675</v>
       </c>
       <c r="B109" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>135403869</v>
       </c>
       <c r="B110" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>135403891</v>
       </c>
       <c r="B111" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>135403907</v>
       </c>
       <c r="B112" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>135403908</v>
       </c>
       <c r="B113" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>135404006</v>
       </c>
       <c r="B114" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>135404010</v>
       </c>
       <c r="B115" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>135404011</v>
       </c>
       <c r="B116" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>135404430</v>
       </c>
       <c r="B117" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>135404435</v>
       </c>
       <c r="B118" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>135408028</v>
       </c>
       <c r="B119" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>135403903</v>
       </c>
       <c r="B120" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>135403904</v>
       </c>
       <c r="B125" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>135404008</v>
       </c>
       <c r="B126" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>135504173</v>
       </c>
       <c r="B127" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>135404438</v>
       </c>
       <c r="B128" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>135402511</v>
       </c>
       <c r="B129" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>135402514</v>
       </c>
       <c r="B130" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>135402517</v>
       </c>
       <c r="B131" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>135402524</v>
       </c>
       <c r="B132" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>135402533</v>
       </c>
       <c r="B133" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135404013</v>
       </c>
       <c r="B134" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>135404419</v>
       </c>
       <c r="B135" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>135404442</v>
       </c>
       <c r="B136" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>135408015</v>
       </c>
       <c r="B137" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>135408025</v>
       </c>
       <c r="B138" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>135408145</v>
       </c>
       <c r="B139" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>135408147</v>
       </c>
       <c r="B140" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>135403871</v>
       </c>
       <c r="B141" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>135403897</v>
       </c>
       <c r="B142" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>135403910</v>
       </c>
       <c r="B143" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>135404019</v>
       </c>
       <c r="B144" t="n">
-        <v>92407</v>
+        <v>92434</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>135403671</v>
       </c>
       <c r="B145" t="n">
-        <v>93334</v>
+        <v>93361</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>135403898</v>
       </c>
       <c r="B146" t="n">
-        <v>93334</v>
+        <v>93361</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>135404016</v>
       </c>
       <c r="B147" t="n">
-        <v>93334</v>
+        <v>93361</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135404433</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135404447</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>135403885</v>
       </c>
       <c r="B13" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135404423</v>
       </c>
       <c r="B14" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135404444</v>
       </c>
       <c r="B15" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>135403999</v>
       </c>
       <c r="B16" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135404431</v>
       </c>
       <c r="B17" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135408020</v>
       </c>
       <c r="B18" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>135408026</v>
       </c>
       <c r="B19" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135403674</v>
       </c>
       <c r="B20" t="n">
-        <v>93337</v>
+        <v>93339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135408029</v>
       </c>
       <c r="B22" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>135402506</v>
       </c>
       <c r="B25" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>135402508</v>
       </c>
       <c r="B26" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>135402510</v>
       </c>
       <c r="B27" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135402512</v>
       </c>
       <c r="B28" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>135402515</v>
       </c>
       <c r="B29" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135402518</v>
       </c>
       <c r="B30" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>135402519</v>
       </c>
       <c r="B31" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>135402522</v>
       </c>
       <c r="B32" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>135402523</v>
       </c>
       <c r="B33" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>135402525</v>
       </c>
       <c r="B34" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>135402526</v>
       </c>
       <c r="B35" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>135402527</v>
       </c>
       <c r="B36" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135402528</v>
       </c>
       <c r="B37" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>135402530</v>
       </c>
       <c r="B38" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>135402531</v>
       </c>
       <c r="B39" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>135402532</v>
       </c>
       <c r="B40" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>135403667</v>
       </c>
       <c r="B41" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>135403672</v>
       </c>
       <c r="B42" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>135403868</v>
       </c>
       <c r="B43" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>135403870</v>
       </c>
       <c r="B44" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135403872</v>
       </c>
       <c r="B45" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>135403873</v>
       </c>
       <c r="B46" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>135403876</v>
       </c>
       <c r="B47" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>135403878</v>
       </c>
       <c r="B48" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>135403881</v>
       </c>
       <c r="B49" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>135403884</v>
       </c>
       <c r="B50" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135403894</v>
       </c>
       <c r="B51" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>135403896</v>
       </c>
       <c r="B52" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>135403899</v>
       </c>
       <c r="B53" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>135403901</v>
       </c>
       <c r="B54" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135403909</v>
       </c>
       <c r="B55" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135403911</v>
       </c>
       <c r="B56" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>135404004</v>
       </c>
       <c r="B57" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>135404005</v>
       </c>
       <c r="B58" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>135404014</v>
       </c>
       <c r="B59" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>135404015</v>
       </c>
       <c r="B60" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>135404018</v>
       </c>
       <c r="B61" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>135404420</v>
       </c>
       <c r="B62" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>135404421</v>
       </c>
       <c r="B63" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135404424</v>
       </c>
       <c r="B64" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135404425</v>
       </c>
       <c r="B65" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>135404426</v>
       </c>
       <c r="B66" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>135404428</v>
       </c>
       <c r="B67" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135404429</v>
       </c>
       <c r="B68" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>135404437</v>
       </c>
       <c r="B69" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>135404440</v>
       </c>
       <c r="B70" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135404443</v>
       </c>
       <c r="B71" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>135408007</v>
       </c>
       <c r="B72" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>135408008</v>
       </c>
       <c r="B73" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>135408009</v>
       </c>
       <c r="B74" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>135408011</v>
       </c>
       <c r="B75" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135408012</v>
       </c>
       <c r="B76" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>135408013</v>
       </c>
       <c r="B77" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>135408017</v>
       </c>
       <c r="B78" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>135408018</v>
       </c>
       <c r="B79" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>135408023</v>
       </c>
       <c r="B80" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>135408027</v>
       </c>
       <c r="B81" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>135408143</v>
       </c>
       <c r="B82" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>135410054</v>
       </c>
       <c r="B83" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>135410055</v>
       </c>
       <c r="B84" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>135410056</v>
       </c>
       <c r="B85" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>135504175</v>
       </c>
       <c r="B86" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>135403669</v>
       </c>
       <c r="B87" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>135403874</v>
       </c>
       <c r="B88" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>135403875</v>
       </c>
       <c r="B89" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>135403880</v>
       </c>
       <c r="B90" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>135403889</v>
       </c>
       <c r="B91" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>135403895</v>
       </c>
       <c r="B92" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>135402504</v>
       </c>
       <c r="B94" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>135403670</v>
       </c>
       <c r="B95" t="n">
-        <v>93374</v>
+        <v>93376</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>135404019</v>
       </c>
       <c r="B144" t="n">
-        <v>92439</v>
+        <v>92441</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>135403671</v>
       </c>
       <c r="B145" t="n">
-        <v>93366</v>
+        <v>93368</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>135403898</v>
       </c>
       <c r="B146" t="n">
-        <v>93366</v>
+        <v>93368</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>135404016</v>
       </c>
       <c r="B147" t="n">
-        <v>93366</v>
+        <v>93368</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135404433</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135404447</v>
       </c>
       <c r="B3" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135403886</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135403890</v>
       </c>
       <c r="B5" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135403893</v>
       </c>
       <c r="B6" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135403912</v>
       </c>
       <c r="B7" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135404432</v>
       </c>
       <c r="B8" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135404446</v>
       </c>
       <c r="B9" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135408019</v>
       </c>
       <c r="B10" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135404434</v>
       </c>
       <c r="B12" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>135403885</v>
       </c>
       <c r="B13" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135404423</v>
       </c>
       <c r="B14" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135404444</v>
       </c>
       <c r="B15" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>135403999</v>
       </c>
       <c r="B16" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135404431</v>
       </c>
       <c r="B17" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135408020</v>
       </c>
       <c r="B18" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>135408026</v>
       </c>
       <c r="B19" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135403674</v>
       </c>
       <c r="B20" t="n">
-        <v>93339</v>
+        <v>93354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135408029</v>
       </c>
       <c r="B22" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>135402506</v>
       </c>
       <c r="B25" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>135402508</v>
       </c>
       <c r="B26" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>135402510</v>
       </c>
       <c r="B27" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135402512</v>
       </c>
       <c r="B28" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>135402515</v>
       </c>
       <c r="B29" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>135402518</v>
       </c>
       <c r="B30" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>135402519</v>
       </c>
       <c r="B31" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>135402522</v>
       </c>
       <c r="B32" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>135402523</v>
       </c>
       <c r="B33" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>135402525</v>
       </c>
       <c r="B34" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>135402526</v>
       </c>
       <c r="B35" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>135402527</v>
       </c>
       <c r="B36" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135402528</v>
       </c>
       <c r="B37" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>135402530</v>
       </c>
       <c r="B38" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>135402531</v>
       </c>
       <c r="B39" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>135402532</v>
       </c>
       <c r="B40" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>135403667</v>
       </c>
       <c r="B41" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>135403672</v>
       </c>
       <c r="B42" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>135403868</v>
       </c>
       <c r="B43" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>135403870</v>
       </c>
       <c r="B44" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>135403872</v>
       </c>
       <c r="B45" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>135403873</v>
       </c>
       <c r="B46" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>135403876</v>
       </c>
       <c r="B47" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>135403878</v>
       </c>
       <c r="B48" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>135403881</v>
       </c>
       <c r="B49" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>135403884</v>
       </c>
       <c r="B50" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135403894</v>
       </c>
       <c r="B51" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>135403896</v>
       </c>
       <c r="B52" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>135403899</v>
       </c>
       <c r="B53" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>135403901</v>
       </c>
       <c r="B54" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135403909</v>
       </c>
       <c r="B55" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135403911</v>
       </c>
       <c r="B56" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>135404004</v>
       </c>
       <c r="B57" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>135404005</v>
       </c>
       <c r="B58" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>135404014</v>
       </c>
       <c r="B59" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>135404015</v>
       </c>
       <c r="B60" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>135404018</v>
       </c>
       <c r="B61" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>135404420</v>
       </c>
       <c r="B62" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>135404421</v>
       </c>
       <c r="B63" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135404424</v>
       </c>
       <c r="B64" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135404425</v>
       </c>
       <c r="B65" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>135404426</v>
       </c>
       <c r="B66" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>135404428</v>
       </c>
       <c r="B67" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135404429</v>
       </c>
       <c r="B68" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>135404437</v>
       </c>
       <c r="B69" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>135404440</v>
       </c>
       <c r="B70" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135404443</v>
       </c>
       <c r="B71" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>135408007</v>
       </c>
       <c r="B72" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>135408008</v>
       </c>
       <c r="B73" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>135408009</v>
       </c>
       <c r="B74" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>135408011</v>
       </c>
       <c r="B75" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135408012</v>
       </c>
       <c r="B76" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>135408013</v>
       </c>
       <c r="B77" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>135408017</v>
       </c>
       <c r="B78" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>135408018</v>
       </c>
       <c r="B79" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>135408023</v>
       </c>
       <c r="B80" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>135408027</v>
       </c>
       <c r="B81" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>135408143</v>
       </c>
       <c r="B82" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>135410054</v>
       </c>
       <c r="B83" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>135410055</v>
       </c>
       <c r="B84" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>135410056</v>
       </c>
       <c r="B85" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>135504175</v>
       </c>
       <c r="B86" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>135403669</v>
       </c>
       <c r="B87" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>135403874</v>
       </c>
       <c r="B88" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>135403875</v>
       </c>
       <c r="B89" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>135403880</v>
       </c>
       <c r="B90" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>135403889</v>
       </c>
       <c r="B91" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>135403895</v>
       </c>
       <c r="B92" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>135402504</v>
       </c>
       <c r="B94" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>135403670</v>
       </c>
       <c r="B95" t="n">
-        <v>93376</v>
+        <v>93391</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>135408010</v>
       </c>
       <c r="B96" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>135408016</v>
       </c>
       <c r="B97" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>135402521</v>
       </c>
       <c r="B98" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>135403892</v>
       </c>
       <c r="B99" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>135403902</v>
       </c>
       <c r="B100" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>135404009</v>
       </c>
       <c r="B101" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>135404427</v>
       </c>
       <c r="B102" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>135404436</v>
       </c>
       <c r="B103" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>135404439</v>
       </c>
       <c r="B104" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>135403900</v>
       </c>
       <c r="B105" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>135404007</v>
       </c>
       <c r="B106" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>135402513</v>
       </c>
       <c r="B107" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>135402520</v>
       </c>
       <c r="B108" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>135403675</v>
       </c>
       <c r="B109" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>135403869</v>
       </c>
       <c r="B110" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>135403891</v>
       </c>
       <c r="B111" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>135403907</v>
       </c>
       <c r="B112" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>135403908</v>
       </c>
       <c r="B113" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>135404006</v>
       </c>
       <c r="B114" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>135404010</v>
       </c>
       <c r="B115" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>135404011</v>
       </c>
       <c r="B116" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>135404430</v>
       </c>
       <c r="B117" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>135404435</v>
       </c>
       <c r="B118" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>135408028</v>
       </c>
       <c r="B119" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>135403903</v>
       </c>
       <c r="B120" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>135402507</v>
       </c>
       <c r="B121" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>135402516</v>
       </c>
       <c r="B122" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>135404441</v>
       </c>
       <c r="B123" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>135404422</v>
       </c>
       <c r="B124" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>135403904</v>
       </c>
       <c r="B125" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>135404008</v>
       </c>
       <c r="B126" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>135504173</v>
       </c>
       <c r="B127" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>135404438</v>
       </c>
       <c r="B128" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>135402511</v>
       </c>
       <c r="B129" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>135402514</v>
       </c>
       <c r="B130" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>135402517</v>
       </c>
       <c r="B131" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>135402524</v>
       </c>
       <c r="B132" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>135402533</v>
       </c>
       <c r="B133" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>135404013</v>
       </c>
       <c r="B134" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>135404419</v>
       </c>
       <c r="B135" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>135404442</v>
       </c>
       <c r="B136" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>135408015</v>
       </c>
       <c r="B137" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>135408025</v>
       </c>
       <c r="B138" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>135408145</v>
       </c>
       <c r="B139" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>135408147</v>
       </c>
       <c r="B140" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>135403871</v>
       </c>
       <c r="B141" t="n">
-        <v>80335</v>
+        <v>80337</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>135403897</v>
       </c>
       <c r="B142" t="n">
-        <v>80335</v>
+        <v>80337</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>135403910</v>
       </c>
       <c r="B143" t="n">
-        <v>80335</v>
+        <v>80337</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>135404019</v>
       </c>
       <c r="B144" t="n">
-        <v>92441</v>
+        <v>92455</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>135403671</v>
       </c>
       <c r="B145" t="n">
-        <v>93368</v>
+        <v>93383</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>135403898</v>
       </c>
       <c r="B146" t="n">
-        <v>93368</v>
+        <v>93383</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>135404016</v>
       </c>
       <c r="B147" t="n">
-        <v>93368</v>
+        <v>93383</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 26668-2026 artfynd.xlsx
+++ b/artfynd/A 26668-2026 artfynd.xlsx
@@ -10073,7 +10073,7 @@
         <v>135504175</v>
       </c>
       <c r="B86" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>135504173</v>
       </c>
       <c r="B127" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>135408145</v>
       </c>
       <c r="B139" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
